--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="121">
   <si>
     <t>Mat</t>
   </si>
@@ -97,142 +97,169 @@
     <t>BONILLA</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>VALENTE</t>
   </si>
   <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>TERRAZAS</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>GROT</t>
+  </si>
+  <si>
+    <t>PULIDO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>AMAYO</t>
+  </si>
+  <si>
+    <t>VIDERIQUE</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>AMAYO</t>
-  </si>
-  <si>
-    <t>VIDERIQUE</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>ZARATE</t>
   </si>
   <si>
     <t>TORRES</t>
@@ -250,88 +277,106 @@
     <t>FERNANDA MARGARITA</t>
   </si>
   <si>
+    <t>AMALIA PAULINA</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
     <t>JUAN EMANUEL</t>
   </si>
   <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
     <t>ARTHUR RICHARD</t>
   </si>
   <si>
     <t>AARON MIGUEL</t>
   </si>
   <si>
-    <t>ANGEL CHARBEL</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAIR</t>
+  </si>
+  <si>
+    <t>JORGE MARIO</t>
   </si>
   <si>
     <t>AMISADAI</t>
   </si>
   <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
     <t>CRISTOPHER</t>
   </si>
   <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
     <t>ANA LAURA</t>
   </si>
   <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>NAHUM HIRAM</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>JULISSA MICHELLE</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>DYLAN</t>
+  </si>
+  <si>
+    <t>BELEN</t>
+  </si>
+  <si>
+    <t>ABIEL NEFTALI</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>MARIA REYNA</t>
+  </si>
+  <si>
+    <t>ADALY</t>
+  </si>
+  <si>
+    <t>NEIL</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>LUIS CARLOS</t>
+  </si>
+  <si>
+    <t>ANETTE JOCELYN</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>OLIVA</t>
+  </si>
+  <si>
+    <t>ROSA JAZMIN</t>
+  </si>
+  <si>
     <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>LILIAN</t>
-  </si>
-  <si>
-    <t>JULISSA MICHELLE</t>
-  </si>
-  <si>
-    <t>DYLAN</t>
-  </si>
-  <si>
-    <t>BELEN</t>
-  </si>
-  <si>
-    <t>ABIEL NEFTALI</t>
-  </si>
-  <si>
-    <t>JUAN GERARDO</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>NEIL</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>ROSA JAZMIN</t>
   </si>
   <si>
     <t>ROSA ITZEL</t>
@@ -1002,16 +1047,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>46.34</v>
+      </c>
+      <c r="H4">
+        <v>6.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1025,16 +1073,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>54.84</v>
+      </c>
+      <c r="H5">
+        <v>6.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1048,16 +1099,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>86.84</v>
+      </c>
+      <c r="H6">
+        <v>7.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1071,16 +1125,19 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>64.29000000000001</v>
+      </c>
+      <c r="H7">
+        <v>5.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1094,16 +1151,19 @@
         <v>41</v>
       </c>
       <c r="D8">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>58.54</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1211,16 +1271,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>58.54</v>
+        <v>46.34</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1237,16 +1297,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>74.19</v>
+        <v>54.84</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1263,13 +1323,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>92.11</v>
+        <v>86.84</v>
       </c>
       <c r="H6">
         <v>7.3</v>
@@ -1298,7 +1358,7 @@
         <v>64.29000000000001</v>
       </c>
       <c r="H7">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1315,16 +1375,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>68.29000000000001</v>
+        <v>58.54</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
   </sheetData>
@@ -1334,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1372,10 +1432,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1395,10 +1455,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1418,10 +1478,10 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1435,16 +1495,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920401</v>
+        <v>22330051920240</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1458,22 +1518,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920031</v>
+        <v>22330051920251</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1481,22 +1541,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920034</v>
+        <v>22330051920401</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1510,10 +1570,10 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1533,10 +1593,10 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1550,22 +1610,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920050</v>
+        <v>21330051920156</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1573,22 +1633,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920203</v>
+        <v>21330051920165</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1596,22 +1656,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920298</v>
+        <v>21330051920166</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1619,22 +1679,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920299</v>
+        <v>21330051920189</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1642,22 +1702,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920337</v>
+        <v>21330051920209</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1665,16 +1725,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920316</v>
+        <v>21330051920298</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1688,16 +1748,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920321</v>
+        <v>21330051920337</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1711,16 +1771,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920323</v>
+        <v>21330051920321</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1734,39 +1794,39 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920378</v>
+        <v>21330051920328</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920200</v>
+        <v>22330051920378</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1780,22 +1840,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051420317</v>
+        <v>22330051920200</v>
       </c>
       <c r="B20" t="s">
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1803,16 +1863,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920249</v>
+        <v>21330051420317</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1832,10 +1892,10 @@
         <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1849,22 +1909,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920035</v>
+        <v>22330051920257</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1872,16 +1932,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920141</v>
+        <v>22330051920035</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1895,16 +1955,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920047</v>
+        <v>22330051920141</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1918,22 +1978,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920156</v>
+        <v>22330051920047</v>
       </c>
       <c r="B26" t="s">
         <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1947,10 +2007,10 @@
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1964,22 +2024,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920187</v>
+        <v>21330051920180</v>
       </c>
       <c r="B28" t="s">
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1987,22 +2047,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920212</v>
+        <v>21330051920181</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2010,22 +2070,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920289</v>
+        <v>21330051920187</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2033,16 +2093,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920235</v>
+        <v>21330051920289</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -2056,16 +2116,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920315</v>
+        <v>21330051920301</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -2079,16 +2139,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920330</v>
+        <v>21330051920306</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -2097,6 +2157,144 @@
         <v>16</v>
       </c>
       <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>20330051920235</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>21330051920307</v>
+      </c>
+      <c r="B35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>21330051920090</v>
+      </c>
+      <c r="B36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" t="s">
+        <v>117</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>21330051920315</v>
+      </c>
+      <c r="B37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>21330051920323</v>
+      </c>
+      <c r="B38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>21330051920330</v>
+      </c>
+      <c r="B39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" t="s">
+        <v>120</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="120">
   <si>
     <t>Mat</t>
   </si>
@@ -88,163 +88,163 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>VERA</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
   </si>
   <si>
     <t>BONILLA</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>REYES</t>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>TERRAZAS</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>GROT</t>
   </si>
   <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>TERRAZAS</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
+    <t>PULIDO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
   </si>
   <si>
     <t>MARQUEZ</t>
   </si>
   <si>
-    <t>GROT</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>AMAYO</t>
-  </si>
-  <si>
-    <t>VIDERIQUE</t>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
   </si>
   <si>
     <t>MIXCOA</t>
@@ -268,76 +268,73 @@
     <t>ESPINDOLA</t>
   </si>
   <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>FERNANDA MARGARITA</t>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>NAHUM HIRAM</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>JULISSA MICHELLE</t>
+  </si>
+  <si>
+    <t>JUAN EMANUEL</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAIR</t>
+  </si>
+  <si>
+    <t>JORGE MARIO</t>
+  </si>
+  <si>
+    <t>AMISADAI</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
   </si>
   <si>
     <t>AMALIA PAULINA</t>
   </si>
   <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>JUAN GERARDO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAIR</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
     <t>SERGIO</t>
   </si>
   <si>
-    <t>JULISSA MICHELLE</t>
-  </si>
-  <si>
     <t>KAREN</t>
   </si>
   <si>
-    <t>DYLAN</t>
-  </si>
-  <si>
-    <t>BELEN</t>
+    <t>MIGUEL ANTONIO</t>
+  </si>
+  <si>
+    <t>KARLA ABIGAIL</t>
   </si>
   <si>
     <t>ABIEL NEFTALI</t>
@@ -1001,16 +998,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>59.46</v>
+      </c>
+      <c r="H2">
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1024,16 +1024,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>35.48</v>
+      </c>
+      <c r="H3">
+        <v>5.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1219,16 +1222,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>62.16</v>
+        <v>59.46</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1245,16 +1248,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>48.39</v>
+        <v>35.48</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1394,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1426,13 +1429,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920180</v>
+        <v>22330051920188</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
         <v>83</v>
@@ -1449,13 +1452,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920371</v>
+        <v>22330051920200</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
         <v>84</v>
@@ -1472,13 +1475,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920233</v>
+        <v>22330051920369</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
         <v>85</v>
@@ -1495,13 +1498,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920240</v>
+        <v>22330051920251</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
         <v>86</v>
@@ -1518,13 +1521,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920251</v>
+        <v>22330051920400</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
         <v>87</v>
@@ -1547,7 +1550,7 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
         <v>88</v>
@@ -1564,13 +1567,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920189</v>
+        <v>22330051920031</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
         <v>89</v>
@@ -1587,13 +1590,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920043</v>
+        <v>22330051920034</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
         <v>90</v>
@@ -1610,22 +1613,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920156</v>
+        <v>22330051920189</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
         <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1633,13 +1636,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920165</v>
+        <v>21330051920156</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
         <v>92</v>
@@ -1656,13 +1659,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920166</v>
+        <v>21330051920165</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
         <v>93</v>
@@ -1679,13 +1682,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920189</v>
+        <v>21330051920166</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
         <v>94</v>
@@ -1694,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1702,13 +1705,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920209</v>
+        <v>21330051920189</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
         <v>95</v>
@@ -1725,13 +1728,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920298</v>
+        <v>21330051920209</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
         <v>96</v>
@@ -1740,7 +1743,7 @@
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1748,13 +1751,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920337</v>
+        <v>21330051920298</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
         <v>97</v>
@@ -1771,13 +1774,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920321</v>
+        <v>21330051920337</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
         <v>98</v>
@@ -1794,10 +1797,10 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920328</v>
+        <v>21330051920321</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
         <v>69</v>
@@ -1820,7 +1823,7 @@
         <v>22330051920378</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
         <v>70</v>
@@ -1840,10 +1843,10 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920200</v>
+        <v>22330051920240</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
         <v>71</v>
@@ -1855,7 +1858,7 @@
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1866,7 +1869,7 @@
         <v>21330051420317</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
         <v>72</v>
@@ -1886,13 +1889,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920400</v>
+        <v>22330051920257</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
         <v>103</v>
@@ -1909,13 +1912,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920257</v>
+        <v>22330051920038</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D23" t="s">
         <v>104</v>
@@ -1924,7 +1927,7 @@
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1932,13 +1935,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920035</v>
+        <v>22330051920041</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
         <v>105</v>
@@ -1955,13 +1958,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920141</v>
+        <v>22330051920047</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s">
         <v>106</v>
@@ -1978,22 +1981,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920047</v>
+        <v>21330051920164</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D26" t="s">
         <v>107</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2001,13 +2004,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920164</v>
+        <v>21330051920180</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
         <v>108</v>
@@ -2024,13 +2027,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920180</v>
+        <v>21330051920181</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -2047,13 +2050,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920181</v>
+        <v>21330051920187</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
         <v>110</v>
@@ -2062,7 +2065,7 @@
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2070,13 +2073,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920187</v>
+        <v>21330051920289</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
         <v>111</v>
@@ -2085,7 +2088,7 @@
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2093,13 +2096,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920289</v>
+        <v>21330051920301</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
         <v>112</v>
@@ -2116,13 +2119,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920301</v>
+        <v>21330051920306</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s">
         <v>113</v>
@@ -2139,13 +2142,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920306</v>
+        <v>20330051920235</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
         <v>114</v>
@@ -2162,13 +2165,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920235</v>
+        <v>21330051920307</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
         <v>115</v>
@@ -2185,13 +2188,13 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920307</v>
+        <v>21330051920090</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
         <v>116</v>
@@ -2208,13 +2211,13 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920090</v>
+        <v>21330051920315</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
         <v>117</v>
@@ -2231,13 +2234,13 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920315</v>
+        <v>21330051920323</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
         <v>118</v>
@@ -2254,13 +2257,13 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920323</v>
+        <v>21330051920330</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
         <v>119</v>
@@ -2272,29 +2275,6 @@
         <v>16</v>
       </c>
       <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920330</v>
-      </c>
-      <c r="B39" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" t="s">
-        <v>120</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>16</v>
-      </c>
-      <c r="G39">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="127">
   <si>
     <t>Mat</t>
   </si>
@@ -94,7 +94,10 @@
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>HUERTA</t>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>MORALES</t>
@@ -118,12 +121,21 @@
     <t>EVANGELISTA</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>LORENZO</t>
   </si>
   <si>
     <t>MACARIO</t>
   </si>
   <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
@@ -142,9 +154,6 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>LLANOS</t>
   </si>
   <si>
@@ -178,12 +187,6 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
     <t>PALOMARES</t>
   </si>
   <si>
@@ -199,7 +202,10 @@
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>VENTURA</t>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
   </si>
   <si>
     <t>GROT</t>
@@ -214,12 +220,21 @@
     <t>DE LA LUZ</t>
   </si>
   <si>
+    <t>MONGE</t>
+  </si>
+  <si>
     <t>ROSETE</t>
   </si>
   <si>
     <t>NERI</t>
   </si>
   <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
@@ -232,9 +247,6 @@
     <t>PLIEGO</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
@@ -274,7 +286,10 @@
     <t>NAHUM HIRAM</t>
   </si>
   <si>
-    <t>NIDIA GABRIELA</t>
+    <t>AZURA</t>
+  </si>
+  <si>
+    <t>AMALIA PAULINA</t>
   </si>
   <si>
     <t>DANIELA DEL CARMEN</t>
@@ -298,12 +313,21 @@
     <t>JUAN GERARDO</t>
   </si>
   <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
     <t>ROBERTO</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
   </si>
   <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>JHOSUA LEVY</t>
+  </si>
+  <si>
     <t>ANGEL ALDAIR</t>
   </si>
   <si>
@@ -320,9 +344,6 @@
   </si>
   <si>
     <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
   </si>
   <si>
     <t>SERGIO</t>
@@ -1397,7 +1418,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1435,10 +1456,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1458,10 +1479,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1475,16 +1496,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920369</v>
+        <v>22330051920230</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1498,16 +1519,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920251</v>
+        <v>22330051920240</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1521,16 +1542,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920400</v>
+        <v>22330051920251</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1544,16 +1565,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920401</v>
+        <v>22330051920400</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1567,22 +1588,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920031</v>
+        <v>22330051920401</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1590,16 +1611,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920034</v>
+        <v>22330051920031</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1613,16 +1634,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920189</v>
+        <v>22330051920034</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1636,22 +1657,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920156</v>
+        <v>22330051920189</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1659,16 +1680,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920165</v>
+        <v>21330051920156</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1682,16 +1703,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920166</v>
+        <v>21330051920163</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1705,22 +1726,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920189</v>
+        <v>21330051920165</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1728,22 +1749,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920209</v>
+        <v>21330051920166</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1751,22 +1772,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920298</v>
+        <v>21330051920171</v>
       </c>
       <c r="B16" t="s">
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1774,22 +1795,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920337</v>
+        <v>21330051920175</v>
       </c>
       <c r="B17" t="s">
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1797,22 +1818,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920321</v>
+        <v>21330051920189</v>
       </c>
       <c r="B18" t="s">
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1820,114 +1841,114 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920378</v>
+        <v>21330051920209</v>
       </c>
       <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920240</v>
+        <v>21330051920298</v>
       </c>
       <c r="B20" t="s">
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051420317</v>
+        <v>21330051920337</v>
       </c>
       <c r="B21" t="s">
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920257</v>
+        <v>21330051920321</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920038</v>
+        <v>22330051920378</v>
       </c>
       <c r="B23" t="s">
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1935,22 +1956,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920041</v>
+        <v>21330051420317</v>
       </c>
       <c r="B24" t="s">
         <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1958,22 +1979,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920047</v>
+        <v>22330051920257</v>
       </c>
       <c r="B25" t="s">
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1981,22 +2002,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920164</v>
+        <v>22330051920038</v>
       </c>
       <c r="B26" t="s">
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2004,22 +2025,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920180</v>
+        <v>22330051920041</v>
       </c>
       <c r="B27" t="s">
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2027,22 +2048,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920181</v>
+        <v>22330051920047</v>
       </c>
       <c r="B28" t="s">
         <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2050,22 +2071,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920187</v>
+        <v>21330051920164</v>
       </c>
       <c r="B29" t="s">
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2073,22 +2094,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920289</v>
+        <v>21330051920180</v>
       </c>
       <c r="B30" t="s">
         <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2096,7 +2117,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920301</v>
+        <v>21330051920181</v>
       </c>
       <c r="B31" t="s">
         <v>52</v>
@@ -2105,13 +2126,13 @@
         <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2119,22 +2140,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920306</v>
+        <v>21330051920187</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2142,16 +2163,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920235</v>
+        <v>21330051920289</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -2165,16 +2186,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920307</v>
+        <v>21330051920301</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -2188,16 +2209,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920090</v>
+        <v>21330051920306</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -2211,16 +2232,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920315</v>
+        <v>20330051920235</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -2234,16 +2255,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920323</v>
+        <v>21330051920307</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
@@ -2257,16 +2278,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920330</v>
+        <v>21330051920090</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D38" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -2275,6 +2296,75 @@
         <v>16</v>
       </c>
       <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>21330051920315</v>
+      </c>
+      <c r="B39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>21330051920323</v>
+      </c>
+      <c r="B40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>21330051920330</v>
+      </c>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="124">
   <si>
     <t>Mat</t>
   </si>
@@ -124,7 +124,7 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>LORENZO</t>
+    <t>LOYO</t>
   </si>
   <si>
     <t>MACARIO</t>
@@ -169,9 +169,6 @@
     <t>ROBLES</t>
   </si>
   <si>
-    <t>LOYO</t>
-  </si>
-  <si>
     <t>TERRAZAS</t>
   </si>
   <si>
@@ -223,9 +220,6 @@
     <t>MONGE</t>
   </si>
   <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
     <t>NERI</t>
   </si>
   <si>
@@ -316,7 +310,7 @@
     <t>MIGUEL</t>
   </si>
   <si>
-    <t>ROBERTO</t>
+    <t>DIEGO ARMANDO</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
@@ -359,9 +353,6 @@
   </si>
   <si>
     <t>ABIEL NEFTALI</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
   </si>
   <si>
     <t>MARIA REYNA</t>
@@ -1418,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1456,10 +1447,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1479,10 +1470,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1502,10 +1493,10 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1525,10 +1516,10 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1548,10 +1539,10 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1571,10 +1562,10 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1594,10 +1585,10 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1617,10 +1608,10 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1643,7 +1634,7 @@
         <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1666,7 +1657,7 @@
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1686,10 +1677,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1709,10 +1700,10 @@
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1726,16 +1717,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920165</v>
+        <v>21330051920164</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1755,10 +1746,10 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1778,10 +1769,10 @@
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1801,10 +1792,10 @@
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1824,10 +1815,10 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1847,10 +1838,10 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1873,7 +1864,7 @@
         <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1896,7 +1887,7 @@
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1916,10 +1907,10 @@
         <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1939,10 +1930,10 @@
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1962,10 +1953,10 @@
         <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1985,10 +1976,10 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2008,10 +1999,10 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2031,10 +2022,10 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2057,7 +2048,7 @@
         <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2071,16 +2062,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920164</v>
+        <v>21330051920180</v>
       </c>
       <c r="B29" t="s">
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D29" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -2094,16 +2085,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920180</v>
+        <v>21330051920181</v>
       </c>
       <c r="B30" t="s">
         <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -2117,22 +2108,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920181</v>
+        <v>21330051920187</v>
       </c>
       <c r="B31" t="s">
         <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2140,22 +2131,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920187</v>
+        <v>21330051920289</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="D32" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2163,16 +2154,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920289</v>
+        <v>21330051920301</v>
       </c>
       <c r="B33" t="s">
         <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -2186,16 +2177,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920301</v>
+        <v>21330051920306</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -2209,16 +2200,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920306</v>
+        <v>20330051920235</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D35" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -2232,16 +2223,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>20330051920235</v>
+        <v>21330051920307</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -2255,16 +2246,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920307</v>
+        <v>21330051920090</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
@@ -2278,16 +2269,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920090</v>
+        <v>21330051920315</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
       </c>
       <c r="D38" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -2301,16 +2292,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>21330051920315</v>
+        <v>21330051920323</v>
       </c>
       <c r="B39" t="s">
         <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
@@ -2324,16 +2315,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>21330051920323</v>
+        <v>21330051920330</v>
       </c>
       <c r="B40" t="s">
         <v>57</v>
       </c>
       <c r="C40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D40" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
@@ -2342,29 +2333,6 @@
         <v>16</v>
       </c>
       <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920330</v>
-      </c>
-      <c r="B41" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" t="s">
-        <v>126</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="143">
   <si>
     <t>Mat</t>
   </si>
@@ -91,34 +91,88 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
   </si>
   <si>
     <t>LOPEZ</t>
@@ -127,13 +181,13 @@
     <t>LOYO</t>
   </si>
   <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>TERRAZAS</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
   </si>
   <si>
     <t>BONILLA</t>
@@ -142,48 +196,9 @@
     <t>RUIZ</t>
   </si>
   <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>TERRAZAS</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>PALOMARES</t>
   </si>
   <si>
@@ -196,37 +211,79 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>PULIDO</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
     <t>MARQUEZ</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>GROT</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
   </si>
   <si>
     <t>MONGE</t>
   </si>
   <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
+    <t>MIXCOA</t>
   </si>
   <si>
     <t>TEXOCO</t>
@@ -235,30 +292,6 @@
     <t>NAVARRO</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -277,34 +310,97 @@
     <t>DAVID</t>
   </si>
   <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>AZURA</t>
+  </si>
+  <si>
+    <t>VANNYA</t>
+  </si>
+  <si>
+    <t>CRHIS AMINADAB</t>
+  </si>
+  <si>
+    <t>JARET</t>
+  </si>
+  <si>
+    <t>JUAN EMANUEL</t>
+  </si>
+  <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>ROGGER JUSEFH</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>JHOSUA LEVY</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>LUIS CARLOS</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>ABDIEL NOE</t>
+  </si>
+  <si>
     <t>NAHUM HIRAM</t>
   </si>
   <si>
-    <t>AZURA</t>
-  </si>
-  <si>
     <t>AMALIA PAULINA</t>
   </si>
   <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
     <t>DANIELA DEL CARMEN</t>
   </si>
   <si>
-    <t>JULISSA MICHELLE</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
+    <t>KAREN</t>
   </si>
   <si>
     <t>RICARDO</t>
   </si>
   <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>JUAN GERARDO</t>
+    <t>MIGUEL ANTONIO</t>
+  </si>
+  <si>
+    <t>ABIEL NEFTALI</t>
   </si>
   <si>
     <t>MIGUEL</t>
@@ -313,13 +409,13 @@
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>JHOSUA LEVY</t>
+    <t>MARIA REYNA</t>
+  </si>
+  <si>
+    <t>ADALY</t>
+  </si>
+  <si>
+    <t>NEIL</t>
   </si>
   <si>
     <t>ANGEL ALDAIR</t>
@@ -328,46 +424,7 @@
     <t>JORGE MARIO</t>
   </si>
   <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>KARLA ABIGAIL</t>
-  </si>
-  <si>
-    <t>ABIEL NEFTALI</t>
-  </si>
-  <si>
-    <t>MARIA REYNA</t>
-  </si>
-  <si>
-    <t>ADALY</t>
-  </si>
-  <si>
-    <t>NEIL</t>
-  </si>
-  <si>
     <t>ANDRES</t>
-  </si>
-  <si>
-    <t>LUIS CARLOS</t>
   </si>
   <si>
     <t>ANETTE JOCELYN</t>
@@ -1409,7 +1466,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1447,10 +1504,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1464,16 +1521,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920200</v>
+        <v>22330051920371</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1493,10 +1550,10 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1510,16 +1567,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920240</v>
+        <v>22330051920232</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1533,16 +1590,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920251</v>
+        <v>22330051920239</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1556,16 +1613,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920400</v>
+        <v>22330051920357</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1582,13 +1639,13 @@
         <v>22330051920401</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1602,16 +1659,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920031</v>
+        <v>22330051920034</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1625,16 +1682,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920034</v>
+        <v>22330051920189</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1648,16 +1705,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920189</v>
+        <v>22330051920039</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1671,22 +1728,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920156</v>
+        <v>22330051920049</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1694,16 +1751,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920163</v>
+        <v>21330051920156</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1717,16 +1774,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920164</v>
+        <v>21330051920165</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1740,16 +1797,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920166</v>
+        <v>21330051920171</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1763,16 +1820,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920171</v>
+        <v>21330051920175</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1786,22 +1843,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920175</v>
+        <v>21330051920199</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1809,16 +1866,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920189</v>
+        <v>21330051920201</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1832,16 +1889,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920209</v>
+        <v>21330051920203</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1855,22 +1912,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920298</v>
+        <v>21330051920213</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1881,13 +1938,13 @@
         <v>21330051920337</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1901,16 +1958,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920321</v>
+        <v>21330051920301</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1924,45 +1981,45 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920378</v>
+        <v>21330051920321</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051420317</v>
+        <v>22330051920378</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1970,22 +2027,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920257</v>
+        <v>22330051920180</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1993,22 +2050,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920038</v>
+        <v>22330051920200</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2016,22 +2073,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920041</v>
+        <v>22330051920240</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2039,22 +2096,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920047</v>
+        <v>21330051420317</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2062,22 +2119,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920180</v>
+        <v>22330051920251</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="D29" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2085,22 +2142,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920181</v>
+        <v>22330051920257</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2108,22 +2165,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920187</v>
+        <v>22330051920031</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2131,22 +2188,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920289</v>
+        <v>22330051920038</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="D32" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2154,22 +2211,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920301</v>
+        <v>22330051920047</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="D33" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2177,22 +2234,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920306</v>
+        <v>21330051920163</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D34" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2200,22 +2257,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920235</v>
+        <v>21330051920164</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D35" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2223,22 +2280,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920307</v>
+        <v>21330051920180</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2246,22 +2303,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920090</v>
+        <v>21330051920181</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2269,22 +2326,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920315</v>
+        <v>21330051920187</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2292,22 +2349,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>21330051920323</v>
+        <v>21330051920189</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2315,24 +2372,208 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
+        <v>21330051920209</v>
+      </c>
+      <c r="B40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>21330051920289</v>
+      </c>
+      <c r="B41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" t="s">
+        <v>135</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>21330051920306</v>
+      </c>
+      <c r="B42" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" t="s">
+        <v>136</v>
+      </c>
+      <c r="E42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>20330051920235</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" t="s">
+        <v>137</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>21330051920307</v>
+      </c>
+      <c r="B44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>21330051920090</v>
+      </c>
+      <c r="B45" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" t="s">
+        <v>139</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>21330051920315</v>
+      </c>
+      <c r="B46" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" t="s">
+        <v>94</v>
+      </c>
+      <c r="D46" t="s">
+        <v>140</v>
+      </c>
+      <c r="E46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>21330051920323</v>
+      </c>
+      <c r="B47" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" t="s">
+        <v>141</v>
+      </c>
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
         <v>21330051920330</v>
       </c>
-      <c r="B40" t="s">
-        <v>57</v>
-      </c>
-      <c r="C40" t="s">
-        <v>84</v>
-      </c>
-      <c r="D40" t="s">
-        <v>123</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="B48" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48" t="s">
+        <v>142</v>
+      </c>
+      <c r="E48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" t="s">
         <v>16</v>
       </c>
-      <c r="G40">
+      <c r="G48">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="141">
   <si>
     <t>Mat</t>
   </si>
@@ -109,9 +109,6 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
     <t>LUNA</t>
   </si>
   <si>
@@ -329,9 +326,6 @@
   </si>
   <si>
     <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
   </si>
   <si>
     <t>ROGGER JUSEFH</t>
@@ -1466,7 +1460,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1504,10 +1498,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1527,10 +1521,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1550,10 +1544,10 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1573,10 +1567,10 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1596,10 +1590,10 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1619,10 +1613,10 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1642,10 +1636,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1665,10 +1659,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1682,16 +1676,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920189</v>
+        <v>22330051920039</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1705,7 +1699,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920039</v>
+        <v>22330051920049</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1714,7 +1708,7 @@
         <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1728,7 +1722,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920049</v>
+        <v>21330051920156</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
@@ -1737,13 +1731,13 @@
         <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1751,7 +1745,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920156</v>
+        <v>21330051920165</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -1760,7 +1754,7 @@
         <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1774,7 +1768,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920165</v>
+        <v>21330051920171</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -1783,7 +1777,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1797,7 +1791,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920171</v>
+        <v>21330051920175</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
@@ -1806,7 +1800,7 @@
         <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1820,7 +1814,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920175</v>
+        <v>21330051920199</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
@@ -1829,13 +1823,13 @@
         <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1843,7 +1837,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920199</v>
+        <v>21330051920201</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
@@ -1852,7 +1846,7 @@
         <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1866,7 +1860,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920201</v>
+        <v>21330051920203</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
@@ -1875,7 +1869,7 @@
         <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1889,16 +1883,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920203</v>
+        <v>21330051920213</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
         <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1912,22 +1906,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920213</v>
+        <v>21330051920337</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1935,16 +1929,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920337</v>
+        <v>21330051920301</v>
       </c>
       <c r="B21" t="s">
         <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1958,7 +1952,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920301</v>
+        <v>21330051920321</v>
       </c>
       <c r="B22" t="s">
         <v>41</v>
@@ -1967,7 +1961,7 @@
         <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1981,7 +1975,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920321</v>
+        <v>22330051920378</v>
       </c>
       <c r="B23" t="s">
         <v>42</v>
@@ -1990,30 +1984,30 @@
         <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920378</v>
+        <v>22330051920180</v>
       </c>
       <c r="B24" t="s">
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2027,16 +2021,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920180</v>
+        <v>22330051920200</v>
       </c>
       <c r="B25" t="s">
         <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2050,7 +2044,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920200</v>
+        <v>22330051920240</v>
       </c>
       <c r="B26" t="s">
         <v>45</v>
@@ -2059,13 +2053,13 @@
         <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2073,7 +2067,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920240</v>
+        <v>21330051420317</v>
       </c>
       <c r="B27" t="s">
         <v>46</v>
@@ -2082,7 +2076,7 @@
         <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2096,16 +2090,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051420317</v>
+        <v>22330051920251</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
         <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2119,16 +2113,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920251</v>
+        <v>22330051920257</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
         <v>84</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2142,22 +2136,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920257</v>
+        <v>22330051920031</v>
       </c>
       <c r="B30" t="s">
         <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2165,16 +2159,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920031</v>
+        <v>22330051920038</v>
       </c>
       <c r="B31" t="s">
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2188,16 +2182,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920038</v>
+        <v>22330051920047</v>
       </c>
       <c r="B32" t="s">
         <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2211,22 +2205,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920047</v>
+        <v>21330051920163</v>
       </c>
       <c r="B33" t="s">
         <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2234,16 +2228,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920163</v>
+        <v>21330051920164</v>
       </c>
       <c r="B34" t="s">
         <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="D34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -2257,16 +2251,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920164</v>
+        <v>21330051920180</v>
       </c>
       <c r="B35" t="s">
         <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -2280,16 +2274,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920180</v>
+        <v>21330051920181</v>
       </c>
       <c r="B36" t="s">
         <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -2303,22 +2297,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920181</v>
+        <v>21330051920187</v>
       </c>
       <c r="B37" t="s">
         <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2326,7 +2320,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920187</v>
+        <v>21330051920189</v>
       </c>
       <c r="B38" t="s">
         <v>56</v>
@@ -2335,7 +2329,7 @@
         <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -2349,7 +2343,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>21330051920189</v>
+        <v>21330051920209</v>
       </c>
       <c r="B39" t="s">
         <v>57</v>
@@ -2358,7 +2352,7 @@
         <v>89</v>
       </c>
       <c r="D39" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
@@ -2372,22 +2366,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>21330051920209</v>
+        <v>21330051920289</v>
       </c>
       <c r="B40" t="s">
         <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2395,16 +2389,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>21330051920289</v>
+        <v>21330051920306</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
@@ -2418,16 +2412,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>21330051920306</v>
+        <v>20330051920235</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
         <v>91</v>
       </c>
       <c r="D42" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
@@ -2441,16 +2435,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>20330051920235</v>
+        <v>21330051920307</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C43" t="s">
         <v>92</v>
       </c>
       <c r="D43" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
@@ -2464,16 +2458,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>21330051920307</v>
+        <v>21330051920090</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C44" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
@@ -2487,16 +2481,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>21330051920090</v>
+        <v>21330051920315</v>
       </c>
       <c r="B45" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
@@ -2510,16 +2504,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>21330051920315</v>
+        <v>21330051920323</v>
       </c>
       <c r="B46" t="s">
         <v>60</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E46" t="s">
         <v>9</v>
@@ -2533,16 +2527,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>21330051920323</v>
+        <v>21330051920330</v>
       </c>
       <c r="B47" t="s">
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
@@ -2551,29 +2545,6 @@
         <v>16</v>
       </c>
       <c r="G47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>21330051920330</v>
-      </c>
-      <c r="B48" t="s">
-        <v>62</v>
-      </c>
-      <c r="C48" t="s">
-        <v>95</v>
-      </c>
-      <c r="D48" t="s">
-        <v>142</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>16</v>
-      </c>
-      <c r="G48">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="93">
   <si>
     <t>Mat</t>
   </si>
@@ -94,213 +94,132 @@
     <t>VERA</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZAVALA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>GAMBOA</t>
   </si>
   <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>TERRAZAS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>TERRAZAS</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>GROT</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
   </si>
   <si>
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>MATA</t>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>SOLANO</t>
   </si>
   <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>GROT</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>ESPINDOLA</t>
   </si>
   <si>
@@ -310,133 +229,70 @@
     <t>ISRAEL</t>
   </si>
   <si>
-    <t>AZURA</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
+    <t>ARACELI</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>BRENDA JANELY</t>
+  </si>
+  <si>
+    <t>AXEL GAEL</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>ROGGER JUSEFH</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>JHOSUA LEVY</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
   </si>
   <si>
     <t>CRHIS AMINADAB</t>
   </si>
   <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>JUAN GERARDO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>JHOSUA LEVY</t>
+    <t>AMALIA PAULINA</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>LUISA MARIA</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>LUIS OMAR</t>
+  </si>
+  <si>
+    <t>MARIA REYNA</t>
   </si>
   <si>
     <t>WENCESLAO</t>
   </si>
   <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>LUIS CARLOS</t>
+    <t>ANETTE JOCELYN</t>
   </si>
   <si>
     <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
-  </si>
-  <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>ABIEL NEFTALI</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>MARIA REYNA</t>
-  </si>
-  <si>
-    <t>ADALY</t>
-  </si>
-  <si>
-    <t>NEIL</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAIR</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>OLIVA</t>
-  </si>
-  <si>
-    <t>ROSA JAZMIN</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
   </si>
   <si>
     <t>ROSA ITZEL</t>
@@ -1285,13 +1141,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>59.46</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H2">
         <v>6.4</v>
@@ -1311,16 +1167,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>35.48</v>
+        <v>51.61</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1337,16 +1193,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>46.34</v>
+        <v>58.54</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1363,16 +1219,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>54.84</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1389,16 +1245,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>86.84</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1415,16 +1271,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G7">
-        <v>64.29000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1441,16 +1297,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>58.54</v>
+        <v>73.17</v>
       </c>
       <c r="H8">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -1460,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1498,10 +1354,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1521,10 +1377,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1538,16 +1394,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920230</v>
+        <v>22330051920318</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1561,16 +1417,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920232</v>
+        <v>22330051920366</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1584,16 +1440,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920239</v>
+        <v>22330051920259</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1607,16 +1463,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920357</v>
+        <v>22330051920176</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1630,22 +1486,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920401</v>
+        <v>22330051920031</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1653,16 +1509,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920034</v>
+        <v>22330051920039</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1676,22 +1532,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920039</v>
+        <v>21330051920165</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1699,22 +1555,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920049</v>
+        <v>21330051920175</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1722,22 +1578,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920156</v>
+        <v>21330051920203</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1745,22 +1601,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920165</v>
+        <v>21330051920213</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1768,22 +1624,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920171</v>
+        <v>21330051920323</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1791,206 +1647,206 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920175</v>
+        <v>22330051920378</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920199</v>
+        <v>22330051920239</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920201</v>
+        <v>22330051920240</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920203</v>
+        <v>21330051420317</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920213</v>
+        <v>22330051920246</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920337</v>
+        <v>22330051920251</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920301</v>
+        <v>21330051920167</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920321</v>
+        <v>21330051920180</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920378</v>
+        <v>21330051920199</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1998,22 +1854,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920180</v>
+        <v>21330051920306</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -2021,22 +1877,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920200</v>
+        <v>21330051920321</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2044,507 +1900,24 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920240</v>
+        <v>21330051920330</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051420317</v>
-      </c>
-      <c r="B27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" t="s">
-        <v>120</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920251</v>
-      </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28" t="s">
-        <v>121</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920257</v>
-      </c>
-      <c r="B29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920031</v>
-      </c>
-      <c r="B30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" t="s">
-        <v>123</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920038</v>
-      </c>
-      <c r="B31" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" t="s">
-        <v>85</v>
-      </c>
-      <c r="D31" t="s">
-        <v>124</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920047</v>
-      </c>
-      <c r="B32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920163</v>
-      </c>
-      <c r="B33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" t="s">
-        <v>126</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920164</v>
-      </c>
-      <c r="B34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" t="s">
-        <v>60</v>
-      </c>
-      <c r="D34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920180</v>
-      </c>
-      <c r="B35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" t="s">
-        <v>40</v>
-      </c>
-      <c r="D35" t="s">
-        <v>128</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920181</v>
-      </c>
-      <c r="B36" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" t="s">
-        <v>129</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920187</v>
-      </c>
-      <c r="B37" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" t="s">
-        <v>87</v>
-      </c>
-      <c r="D37" t="s">
-        <v>130</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920189</v>
-      </c>
-      <c r="B38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38" t="s">
-        <v>131</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920209</v>
-      </c>
-      <c r="B39" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" t="s">
-        <v>132</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920289</v>
-      </c>
-      <c r="B40" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" t="s">
-        <v>47</v>
-      </c>
-      <c r="D40" t="s">
-        <v>133</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>16</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920306</v>
-      </c>
-      <c r="B41" t="s">
-        <v>51</v>
-      </c>
-      <c r="C41" t="s">
-        <v>90</v>
-      </c>
-      <c r="D41" t="s">
-        <v>134</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>20330051920235</v>
-      </c>
-      <c r="B42" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" t="s">
-        <v>91</v>
-      </c>
-      <c r="D42" t="s">
-        <v>135</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>16</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21330051920307</v>
-      </c>
-      <c r="B43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" t="s">
-        <v>92</v>
-      </c>
-      <c r="D43" t="s">
-        <v>136</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>16</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>21330051920090</v>
-      </c>
-      <c r="B44" t="s">
-        <v>34</v>
-      </c>
-      <c r="C44" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" t="s">
-        <v>137</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>21330051920315</v>
-      </c>
-      <c r="B45" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45" t="s">
-        <v>93</v>
-      </c>
-      <c r="D45" t="s">
-        <v>138</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>16</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>21330051920323</v>
-      </c>
-      <c r="B46" t="s">
-        <v>60</v>
-      </c>
-      <c r="C46" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" t="s">
-        <v>139</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>16</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>21330051920330</v>
-      </c>
-      <c r="B47" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47" t="s">
-        <v>140</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>16</v>
-      </c>
-      <c r="G47">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="112">
   <si>
     <t>Mat</t>
   </si>
@@ -88,60 +88,81 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZAVALA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZAVALA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>MAYO</t>
   </si>
   <si>
@@ -154,60 +175,69 @@
     <t>ZUÑIGA</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GROT</t>
   </si>
   <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>GROT</t>
-  </si>
-  <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
@@ -223,61 +253,88 @@
     <t>ESPINDOLA</t>
   </si>
   <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>LUZ ALONDRA</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>ARACELI</t>
+  </si>
+  <si>
+    <t>NOEMI DEL ROCIO</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>BRENDA JANELY</t>
+  </si>
+  <si>
+    <t>AXEL GAEL</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>JHOSUA LEVY</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
     <t>DAVID</t>
   </si>
   <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
     <t>ISRAEL</t>
   </si>
   <si>
-    <t>ARACELI</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>BRENDA JANELY</t>
-  </si>
-  <si>
-    <t>AXEL GAEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
+    <t>CRHIS AMINADAB</t>
+  </si>
+  <si>
+    <t>AMALIA PAULINA</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>LUISA MARIA</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
   </si>
   <si>
     <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>JHOSUA LEVY</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
-  </si>
-  <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>LUISA MARIA</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
   </si>
   <si>
     <t>LUIS OMAR</t>
@@ -1316,7 +1373,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1348,16 +1405,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920188</v>
+        <v>22330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1371,16 +1428,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920371</v>
+        <v>22330051920413</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1394,22 +1451,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920318</v>
+        <v>22330051920356</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1417,16 +1474,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920366</v>
+        <v>22330051920233</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1440,16 +1497,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920259</v>
+        <v>22330051920236</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1463,16 +1520,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920176</v>
+        <v>22330051920237</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1486,22 +1543,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920031</v>
+        <v>22330051920369</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1509,22 +1566,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920039</v>
+        <v>22330051920318</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1532,22 +1589,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920165</v>
+        <v>22330051920253</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1555,22 +1612,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920175</v>
+        <v>22330051920366</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1578,22 +1635,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920203</v>
+        <v>22330051920259</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1601,22 +1658,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920213</v>
+        <v>22330051920176</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1624,22 +1681,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920323</v>
+        <v>22330051920031</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1647,160 +1704,160 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920378</v>
+        <v>22330051920045</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920239</v>
+        <v>21330051920165</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920240</v>
+        <v>21330051920175</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051420317</v>
+        <v>21330051920203</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920246</v>
+        <v>21330051920213</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920251</v>
+        <v>21330051920323</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920167</v>
+        <v>22330051920188</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1808,22 +1865,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920180</v>
+        <v>22330051920378</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1831,22 +1888,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920199</v>
+        <v>22330051920371</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1854,22 +1911,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920306</v>
+        <v>22330051920239</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1877,22 +1934,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920321</v>
+        <v>22330051920240</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1900,24 +1957,231 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920330</v>
+        <v>21330051420317</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>22330051920246</v>
+      </c>
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>22330051920251</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>22330051920039</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>21330051920167</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>21330051920180</v>
+      </c>
+      <c r="B31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>21330051920199</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>21330051920306</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
         <v>16</v>
       </c>
-      <c r="G26">
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>21330051920321</v>
+      </c>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" t="s">
+        <v>110</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>21330051920330</v>
+      </c>
+      <c r="B35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35">
         <v>1</v>
       </c>
     </row>
